--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0151.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0151.xlsx
@@ -3824,7 +3824,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>R?i ?i! Ai thèm nhận tờ giấy nợ nguệch ngoạc của ngươi! Ngươi mà dám thề danh dự, thì đừng có quên!</t>
+          <t>Rời đi! Ai thèm nhận tờ giấy nợ nguệch ngoạc của ngươi! Ngươi mà dám thề danh dự, thì đừng có quên!</t>
         </is>
       </c>
     </row>
@@ -24949,7 +24949,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Cậu... Quy tắc có lý do của nó. Không phải thứ để bẻ cong theo ý thích cá nhân đâu.</t>
+          <t>Mày... Quy tắc có lý do của nó. Không phải thứ để bẻ cong theo ý thích cá nhân đâu.</t>
         </is>
       </c>
     </row>
@@ -25079,7 +25079,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Rover à. Ngươi đã đi qua nhiều nơi hơn hầu hết mọi người. Có lẽ ngươi muốn chia sẻ đôi lời?</t>
+          <t>Vận Mệnh Giả à. Ngươi đã đi qua nhiều nơi hơn hầu hết mọi người. Có lẽ ngươi muốn chia sẻ đôi lời?</t>
         </is>
       </c>
     </row>
@@ -26379,7 +26379,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Ôi, cảm ơn cậu. Cảm ơn cậu rất nhiều. Lúc đó đầu óc tôi trống rỗng, không biết phải làm gì. Thật may là cậu đã giúp tôi tìm thấy con bé!</t>
+          <t>Ôi, cảm ơn bạn. Cảm ơn bạn rất nhiều. Lúc đó đầu óc tôi trống rỗng, không biết phải làm gì. Thật may là bạn đã giúp tôi tìm thấy con bé!</t>
         </is>
       </c>
     </row>
@@ -27549,7 +27549,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Yên tĩnh hơn rồi à? Không đâu, ta biết mà. Dù đã về hưu, ông vẫn còn muốn "phục vụ thành phố". Bỏ nhà đi cũng chẳng giải quyết được vấn đề nhà ở của Septimont đâu.</t>
+          <t>Yên tĩnh hơn rồi à? Không đâu, tao biết mà. Dù đã về hưu, ông vẫn còn muốn "phục vụ thành phố". Bỏ nhà đi cũng chẳng giải quyết được vấn đề nhà ở của Septimont đâu.</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Nhưng mà... chúng ta đã cùng nhau trải qua bao nhiêu rồi. Cậu đi đâu, ta đi đó.</t>
+          <t>Nhưng mà... chúng ta đã cùng nhau trải qua bao nhiêu rồi. Cậu đi đâu, tao đi đó.</t>
         </is>
       </c>
     </row>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Cậu vừa nói gì? Chẳng trách họ cứ nhìn chằm chằm vào ta. Cậu bảo ta đứng đó cả buổi như thằng ngốc à!</t>
+          <t>Cậu vừa nói gì? Chẳng trách họ cứ nhìn chằm chằm vào tao. Cậu bảo tao đứng đó cả buổi như thằng ngốc à!</t>
         </is>
       </c>
     </row>
@@ -30734,7 +30734,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Này tôi tớ, cậu có biết hai thằng nhóc kia là ai không? Chúng nó cứ la hét không ngừng ấy.</t>
+          <t>Này tôi tớ, mày có biết hai thằng nhóc kia là ai không? Chúng nó cứ la hét không ngừng ấy.</t>
         </is>
       </c>
     </row>
@@ -31579,7 +31579,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Xuống đây thì tốt hơn cho cậu đấy, Julius. Chôn cả đời trong bùn, theo đuổi những giấc mơ chẳng bao giờ thành hiện thực.</t>
+          <t>Xuống đây thì tốt hơn cho mày đấy, Julius. Chôn cả đời trong bùn, theo đuổi những giấc mơ chẳng bao giờ thành hiện thực.</t>
         </is>
       </c>
     </row>
@@ -32554,7 +32554,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Đây là khu VIP đấy, kẻ hạ đẳng. Ngươi nhầm chỗ rồi. Phòng tắm của ngươi ở tầng dưới kia.</t>
+          <t>Đây là khu VIP đấy, kẻ hạ đẳng. Mày nhầm chỗ rồi. Phòng tắm của mày ở tầng dưới kia.</t>
         </is>
       </c>
     </row>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Hừ. Nhận thức của ngươi định hình góc nhìn của ngươi. Sao một kẻ thấp hèn như ngươi dám bàn về công lao của giới quý tộc chúng ta? Biết thân biết phận đi.</t>
+          <t>Hừ. Nhận thức của mày định hình góc nhìn của mày. Sao một kẻ thấp hèn như mày dám bàn về công lao của giới quý tộc chúng tao? Biết thân biết phận đi.</t>
         </is>
       </c>
     </row>
@@ -33009,7 +33009,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Chết tiệt! Càng cố quên, ta càng bực! Nhượng bộ chỉ khiến ta thấy mình như thằng ngốc!</t>
+          <t>Chết tiệt! Càng cố quên, tao càng bực! Nhượng bộ chỉ khiến tao thấy mình như thằng ngốc!</t>
         </is>
       </c>
     </row>
